--- a/Output/Hourly Scan_19 Jul 2026.xlsx
+++ b/Output/Hourly Scan_19 Jul 2026.xlsx
@@ -19790,7 +19790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19858,272 +19858,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANKIND</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Output/Hourly Scan_19 Jul 2026.xlsx
+++ b/Output/Hourly Scan_19 Jul 2026.xlsx
@@ -32,13 +32,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,12 +60,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,62 +444,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -7420,62 +7432,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -13204,62 +13216,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19308,62 +19320,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19402,62 +19414,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19504,62 +19516,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19606,62 +19618,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19700,62 +19712,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19794,62 +19806,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19888,62 +19900,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -19982,62 +19994,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -20708,62 +20720,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -26400,62 +26412,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -32092,62 +32104,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -38648,62 +38660,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -39954,62 +39966,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
